--- a/Libraries/Vehicle/AntiRollBar/sm_car_data_AntiRollBar_Droplink_Rod.xlsx
+++ b/Libraries/Vehicle/AntiRollBar/sm_car_data_AntiRollBar_Droplink_Rod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\AntiRollBar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C660E8-72A7-47FE-8888-E619283EBEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8EEEAE-AAA0-421C-A0A3-AF35A37F4DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="979" firstSheet="6" activeTab="6" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="3075" yWindow="1995" windowWidth="21600" windowHeight="11295" tabRatio="979" firstSheet="5" activeTab="10" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="Achilles_BC_f" sheetId="11" r:id="rId1"/>
@@ -22,14 +22,18 @@
     <sheet name="Sedan_Hamba_LA_f" sheetId="20" r:id="rId7"/>
     <sheet name="Sedan_Hamba_LA_r" sheetId="21" r:id="rId8"/>
     <sheet name="Sedan_HambaLG_Upr_f" sheetId="13" r:id="rId9"/>
-    <sheet name="Sedan_HambaLG_LA_f" sheetId="22" r:id="rId10"/>
-    <sheet name="Sedan_HambaLG_LA_r" sheetId="23" r:id="rId11"/>
-    <sheet name="Sedan_Hamba_mc_f" sheetId="16" r:id="rId12"/>
-    <sheet name="Sedan_HambaLG_mc_f" sheetId="19" r:id="rId13"/>
-    <sheet name="SUV_Landy_LA_f" sheetId="28" r:id="rId14"/>
-    <sheet name="Bus_Makhulu_mc_f" sheetId="18" r:id="rId15"/>
-    <sheet name="Bus_Makhulu_LA_f" sheetId="24" r:id="rId16"/>
-    <sheet name="Bus_Makhulu_LA_r" sheetId="25" r:id="rId17"/>
+    <sheet name="Sedan_HambaLG_Dam_f" sheetId="29" r:id="rId10"/>
+    <sheet name="Sedan_Hamba_Dam_f" sheetId="31" r:id="rId11"/>
+    <sheet name="Sedan_HambaLG_5LUpr_r" sheetId="30" r:id="rId12"/>
+    <sheet name="Sedan_Hamba_5LUpr_r" sheetId="32" r:id="rId13"/>
+    <sheet name="Sedan_HambaLG_LA_f" sheetId="22" r:id="rId14"/>
+    <sheet name="Sedan_HambaLG_LA_r" sheetId="23" r:id="rId15"/>
+    <sheet name="Sedan_Hamba_mc_f" sheetId="16" r:id="rId16"/>
+    <sheet name="Sedan_HambaLG_mc_f" sheetId="19" r:id="rId17"/>
+    <sheet name="SUV_Landy_LA_f" sheetId="28" r:id="rId18"/>
+    <sheet name="Bus_Makhulu_mc_f" sheetId="18" r:id="rId19"/>
+    <sheet name="Bus_Makhulu_LA_f" sheetId="24" r:id="rId20"/>
+    <sheet name="Bus_Makhulu_LA_r" sheetId="25" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="50">
   <si>
     <t>Units</t>
   </si>
@@ -186,6 +190,21 @@
   <si>
     <t>DroplinkRod_SUV_Landy_LA_f</t>
   </si>
+  <si>
+    <t>DroplinkRod_Sedan_HambaLG_Dam_f</t>
+  </si>
+  <si>
+    <t>Must be same as Linkage.Shock.sARB for attachment to Damper</t>
+  </si>
+  <si>
+    <t>DroplinkRod_Sedan_HambaLG_5LUpr_r</t>
+  </si>
+  <si>
+    <t>DroplinkRod_Sedan_Hamba_Dam_f</t>
+  </si>
+  <si>
+    <t>DroplinkRod_Sedan_Hamba_5LUpr_r</t>
+  </si>
 </sst>
 </file>
 
@@ -303,7 +322,91 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="63">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1247,17 +1350,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1266,6 +1369,1194 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A016A56E-3643-4F98-B87D-6185CF3C2DB8}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2ED4A8-4C23-47B5-BC9C-6BE964C65540}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB5AFC1-B7BB-4F5B-A87F-0B427B238C07}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61433370-21EF-4414-8111-013B40774A8E}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBFBDE5-313F-45A5-9CED-972E63B9DB16}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -1562,7 +2853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5903A62-A942-4A81-A495-B0418FFB493E}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -1859,7 +3150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904101B2-9A7D-48E6-BC19-DD76F7D1310A}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -2154,7 +3445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E15FE28-D7F9-41FC-974A-1C4F83B08D60}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -2451,7 +3742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB21466F-9DF6-4F89-9922-96B5502AE619}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -2752,7 +4043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE304C2-89CE-489F-9A9D-C784A2BF3C11}">
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
@@ -3026,600 +4317,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
     <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E682D2-24ED-4760-8CA2-0BB90F67F0A4}">
-  <sheetPr>
-    <tabColor rgb="FFFF9999"/>
-  </sheetPr>
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="17">
-        <v>-0.05</v>
-      </c>
-      <c r="G5" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="H5" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6">
-        <v>-0.05</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="H19" s="12"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3121048-629F-482E-AE7F-1FD418E93CB2}">
-  <sheetPr>
-    <tabColor rgb="FFFF9999"/>
-  </sheetPr>
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="17">
-        <v>-0.05</v>
-      </c>
-      <c r="G5" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6">
-        <v>-0.05</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="H19" s="12"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3905,17 +4602,611 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="45" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E682D2-24ED-4760-8CA2-0BB90F67F0A4}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3121048-629F-482E-AE7F-1FD418E93CB2}">
+  <sheetPr>
+    <tabColor rgb="FFFF9999"/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A14:B17">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4201,17 +5492,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4497,17 +5788,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4793,17 +6084,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5089,17 +6380,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5386,17 +6677,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5683,17 +6974,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5980,17 +7271,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A19">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B4 A14:B17">
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
